--- a/assumptions_26.xlsx
+++ b/assumptions_26.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.147</v>
+        <v>858499.72</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7039.275</v>
+        <v>602423652.38</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>597000</v>
+        <v>597000000</v>
       </c>
       <c r="C4" t="n">
-        <v>72600</v>
+        <v>54400000</v>
       </c>
       <c r="D4" t="n">
-        <v>669600</v>
+        <v>651400000</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4405.632739999999</v>
+        <v>3321255.54</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>500834.34626</v>
+        <v>267569.2199999997</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>598629.84</v>
+        <v>4334200.73</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93986861</v>
+        <v>597745375.97</v>
       </c>
       <c r="C8" t="n">
-        <v>72600</v>
+        <v>54400000</v>
       </c>
       <c r="D8" t="n">
-        <v>94059461</v>
+        <v>652145375.97</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13730343.03907</v>
+        <v>685597.03</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13824329.90007</v>
+        <v>598430973</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>

--- a/assumptions_26.xlsx
+++ b/assumptions_26.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>858499.72</v>
+        <v>80518234.16</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>602423652.38</v>
+        <v>519134744.05</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3321255.54</v>
+        <v>22418738.06</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>267569.2199999997</v>
+        <v>434137.2799999937</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4334200.73</v>
+        <v>10493226.73</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>597745375.97</v>
+        <v>584640351.3900001</v>
       </c>
       <c r="C8" t="n">
         <v>54400000</v>
       </c>
       <c r="D8" t="n">
-        <v>652145375.97</v>
+        <v>639040351.3900001</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>685597.03</v>
+        <v>469350.12</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>598430973</v>
+        <v>585109701.5100001</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
